--- a/business-libraries/test-data/self_growth/tool.xlsx
+++ b/business-libraries/test-data/self_growth/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AJ7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,82 +430,88 @@
         <v>严重度*</v>
       </c>
       <c r="J1" t="str">
-        <v>对应归因*</v>
+        <v>对应归因编码*</v>
       </c>
       <c r="K1" t="str">
+        <v>对应归因名称</v>
+      </c>
+      <c r="L1" t="str">
         <v>工具标签*</v>
       </c>
-      <c r="L1" t="str">
-        <v>作用维度</v>
-      </c>
       <c r="M1" t="str">
+        <v>作用维度编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>效果说明</v>
+      </c>
+      <c r="O1" t="str">
         <v>操作步骤摘要*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>关键话术</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>预期效果*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>单次耗时</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>疗程与频次</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>重评间隔天数</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>禁止事项*</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>禁忌说明</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>前置工具编码</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>替代工具编码</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>进阶工具编码</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>证据等级*</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>证据来源</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>效果指标</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>失败标准</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>准备事项</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>所需材料</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>输出物</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>协同工具编码</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>SG_RX_001</v>
       </c>
@@ -534,90 +540,99 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>疲惫与意义感同时告急</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="K2" t="str">
-        <v>self_growth,orange,pressure</v>
+        <v>情绪耗竭</v>
       </c>
       <c r="L2" t="str">
-        <v>情绪恢复</v>
+        <v>self_growth,emotion,pressure</v>
       </c>
       <c r="M2" t="str">
-        <v>1) 离开当前情境 2) 三轮缓慢呼吸 3) 命名情绪 4) 选最小行动</v>
+        <v>SG_EMOTION</v>
       </c>
       <c r="N2" t="str">
+        <v>快速降低主观压力，恢复对当下的控制感</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">离开当前情境，找一个不被打扰的空间
+做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒
+给当下的情绪命名，不评价
+选一个 5 分钟内能完成的最小行动</v>
+      </c>
+      <c r="P2" t="str">
         <v>现在先停三分钟，这三分钟只属于你自己。</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>单次可下降 1-2 分主观压力值</v>
       </c>
-      <c r="P2" t="str">
+      <c r="R2" t="str">
         <v>3 分钟</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>每日 1-2 次，连续 7 天</v>
       </c>
-      <c r="R2" t="str">
-        <v>7</v>
-      </c>
-      <c r="S2" t="str">
+      <c r="T2" t="str">
+        <v>30</v>
+      </c>
+      <c r="U2" t="str">
         <v>不用于替代危机处置；出现自伤念头或持续失眠时须转介心理专员</v>
       </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
-        <v/>
-      </c>
       <c r="V2" t="str">
         <v/>
       </c>
       <c r="W2" t="str">
-        <v>SG_RX_004</v>
+        <v/>
       </c>
       <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
         <v>B</v>
       </c>
-      <c r="Y2" t="str">
-        <v>Kabat-Zinn 正念减压研究；教师群体适应性改编研究（2023）</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>主观压力值下降&gt;=1分；一周后情绪耗竭维度得分下降</v>
-      </c>
       <c r="AA2" t="str">
-        <v>连续使用3次后主观压力值未下降</v>
+        <v>Kabat-Zinn 正念减压研究；教师群体适应性改编（2023）</v>
       </c>
       <c r="AB2" t="str">
-        <v>确保教师有3分钟不被打扰的环境</v>
+        <v>主观压力值下降 &gt;= 1 分</v>
       </c>
       <c r="AC2" t="str">
-        <v>计时器、一周能量记录卡</v>
+        <v>连续使用 3 次后主观压力值未下降</v>
       </c>
       <c r="AD2" t="str">
-        <v>一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE2" t="str">
-        <v>SG_RX_004</v>
+        <v>记录表</v>
       </c>
       <c r="AF2" t="str">
-        <v>自我成长赋能处方库 P12</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AI2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH2" t="str">
-        <v>class_system,home_school</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>SG_RX_002</v>
       </c>
       <c r="B3" t="str">
-        <v>能量记录卡</v>
+        <v>压力三分法盘点表</v>
       </c>
       <c r="C3" t="str">
-        <v>能量记录</v>
+        <v>三分法</v>
       </c>
       <c r="D3" t="str">
         <v>self_growth</v>
@@ -632,46 +647,49 @@
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>日常自我照顾和压力管理</v>
+        <v>感到「什么都是我的责任」、任务无法排序时</v>
       </c>
       <c r="I3" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>整体状态偏高</v>
+        <v>SG_AT_BOUNDARY</v>
       </c>
       <c r="K3" t="str">
-        <v>self_growth,orange,selfcare</v>
+        <v>角色边界失守</v>
       </c>
       <c r="L3" t="str">
-        <v>自我照顾</v>
+        <v>self_growth,boundary</v>
       </c>
       <c r="M3" t="str">
-        <v>1) 记录每日能量变化 2) 识别能量消耗源 3) 制定能量补充计划</v>
+        <v>SG_BOUNDARY</v>
       </c>
       <c r="N3" t="str">
-        <v>记录本身就是一种觉察和关爱。</v>
-      </c>
-      <c r="O3" t="str">
-        <v>帮助教师建立自我照顾习惯，降低日常压力水平</v>
+        <v>把弥散的压力转成可操作的清单</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">列出当前所有让你焦虑的事项，不做筛选
+逐项标记为「我能控制」「我能影响」「暂时不可控」
+暂时不可控的一栏整体划掉，本周不再想它
+从「我能控制」里只挑一项，写清今天的第一步</v>
       </c>
       <c r="P3" t="str">
-        <v>5 分钟</v>
+        <v>这件事我会在核实后回复，目前先按约定步骤处理。</v>
       </c>
       <c r="Q3" t="str">
-        <v>每日一次，持续 14 天</v>
+        <v>待处理事项减少三分之一以上</v>
       </c>
       <c r="R3" t="str">
-        <v>14</v>
+        <v>20 分钟</v>
       </c>
       <c r="S3" t="str">
-        <v>本工具不适用于危机情境；教师处于急性心理危机时请先转介心理专员</v>
+        <v>每周一次</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U3" t="str">
-        <v/>
+        <v>不要在盘点时同步处理事项，先列完再动手</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -680,48 +698,54 @@
         <v/>
       </c>
       <c r="X3" t="str">
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y3" t="str">
-        <v>教师自我效能感训练研究（2022）</v>
+        <v/>
       </c>
       <c r="Z3" t="str">
-        <v>连续一周能量记录完整且主观压力值下降</v>
+        <v>C</v>
       </c>
       <c r="AA3" t="str">
-        <v>连续3天未记录</v>
+        <v>教师职业压力管理实务手册</v>
       </c>
       <c r="AB3" t="str">
-        <v>打印一周能量记录卡</v>
+        <v>「暂时不可控」栏目占比 &gt;= 30%</v>
       </c>
       <c r="AC3" t="str">
-        <v>一周能量记录卡、笔</v>
+        <v>连续两周无法把任何事项归入「我能控制」</v>
       </c>
       <c r="AD3" t="str">
-        <v>完成的一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE3" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF3" t="str">
-        <v>自我成长赋能处方库 P15</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AI3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>SG_RX_003</v>
       </c>
       <c r="B4" t="str">
-        <v>同伴支持圈</v>
+        <v>同伴结构化复盘</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴支持</v>
+        <v>同伴复盘</v>
       </c>
       <c r="D4" t="str">
         <v>self_growth</v>
@@ -736,46 +760,49 @@
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>需要同伴支持和经验交流时</v>
+        <v>长期独自承接问题、缺少可求助对象时</v>
       </c>
       <c r="I4" t="str">
-        <v>low</v>
+        <v>high</v>
       </c>
       <c r="J4" t="str">
-        <v>整体状态偏高</v>
+        <v>SG_AT_SUPPORT</v>
       </c>
       <c r="K4" t="str">
-        <v>self_growth,yellow,peer</v>
+        <v>支持系统缺失</v>
       </c>
       <c r="L4" t="str">
-        <v>同伴支持</v>
+        <v>self_growth,support</v>
       </c>
       <c r="M4" t="str">
-        <v>1) 邀请2-3位同事 2) 轮流分享当前困扰 3) 团体生成至少一条行动建议</v>
+        <v>SG_SUPPORT</v>
       </c>
       <c r="N4" t="str">
-        <v>你不是一个人在战斗。</v>
-      </c>
-      <c r="O4" t="str">
-        <v>通过结构化同伴支持缓解教师的孤立感</v>
+        <v>建立稳定的同伴支持通道</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">约一位信任的同事，明确只谈 20 分钟
+按「事实—感受—我需要的支持」三段说，不要求对方给答案
+请对方复述一遍你说的事实，确认没有偏差
+约定下一次复盘时间</v>
       </c>
       <c r="P4" t="str">
-        <v>30 分钟</v>
+        <v>我最近在这个问题上消耗比较大，想请你帮我一起看一下事实和下一步，不需要马上给答案。</v>
       </c>
       <c r="Q4" t="str">
-        <v>每周一次，持续 4 周</v>
+        <v>形成至少一个可定期复盘的同伴关系</v>
       </c>
       <c r="R4" t="str">
-        <v>28</v>
+        <v>20 分钟</v>
       </c>
       <c r="S4" t="str">
-        <v>本活动不等同于心理治疗，涉及严重心理问题时应转介专业支持</v>
+        <v>每两周一次</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U4" t="str">
-        <v/>
+        <v>不要在复盘中评价第三方同事或学生</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -784,54 +811,60 @@
         <v/>
       </c>
       <c r="X4" t="str">
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y4" t="str">
-        <v>同伴支持对教师职业倦怠干预效果研究（2021）</v>
+        <v/>
       </c>
       <c r="Z4" t="str">
-        <v>参与教师反馈压力感和孤立感下降</v>
+        <v>B</v>
       </c>
       <c r="AA4" t="str">
-        <v>连续2次参与人数低于2人</v>
+        <v>教师同伴支持机制研究</v>
       </c>
       <c r="AB4" t="str">
-        <v>准备问题引导卡</v>
+        <v>连续两次完成复盘约定</v>
       </c>
       <c r="AC4" t="str">
-        <v>问题引导卡、白板、记号笔</v>
+        <v>两次邀约均未成行</v>
       </c>
       <c r="AD4" t="str">
-        <v>行动建议记录表</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE4" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF4" t="str">
-        <v>自我成长赋能处方库 P20</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AI4" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>SG_RX_004</v>
       </c>
       <c r="B5" t="str">
-        <v>认知重构练习</v>
+        <v>意义锚点记录</v>
       </c>
       <c r="C5" t="str">
-        <v>认知重构</v>
+        <v>意义锚点</v>
       </c>
       <c r="D5" t="str">
         <v>self_growth</v>
       </c>
       <c r="E5" t="str">
-        <v>script</v>
+        <v>exercise</v>
       </c>
       <c r="F5" t="str">
         <v>all</v>
@@ -840,97 +873,332 @@
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>出现明显负面自动思维时</v>
+        <v>反复怀疑工作价值、对学生进步不再有反应时</v>
       </c>
       <c r="I5" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="J5" t="str">
-        <v>疲惫与意义感同时告急</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="K5" t="str">
-        <v>self_growth,red,cognitive</v>
+        <v>意义感流失</v>
       </c>
       <c r="L5" t="str">
-        <v>认知调整</v>
+        <v>self_growth,meaning</v>
       </c>
       <c r="M5" t="str">
-        <v>1) 识别负面自动思维 2) 检验思维的证据 3) 生成替代性解释 4) 行动计划</v>
+        <v>SG_MEANING</v>
       </c>
       <c r="N5" t="str">
-        <v>想法不一定是事实，让我们一起来看看证据。</v>
-      </c>
-      <c r="O5" t="str">
-        <v>帮助教师识别和调整负面自动思维，降低认知层面的压力</v>
+        <v>重建工作意义的可见证据</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">每天下班前写一句：今天有一件事因为我而不一样
+不追求重大事件，一句问候、一次等待都算
+连续记录七天后回看，圈出最触动你的三条
+把其中一条讲给一位同事听</v>
       </c>
       <c r="P5" t="str">
+        <v>我今天注意到他主动帮同学捡了书，这在两周前是没有的。</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>意义感知题项得分改善 1 分以上</v>
+      </c>
+      <c r="R5" t="str">
+        <v>3 分钟</v>
+      </c>
+      <c r="S5" t="str">
+        <v>每日一次，连续 7 天</v>
+      </c>
+      <c r="T5" t="str">
+        <v>30</v>
+      </c>
+      <c r="U5" t="str">
+        <v>不要把这个练习变成工作总结</v>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v>B</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>积极心理学教师干预研究</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>七天内完成 &gt;= 5 次记录</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>连续三天无法写出任何一条</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>SG_RX_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>最小成功案例复演</v>
+      </c>
+      <c r="C6" t="str">
+        <v>最小复演</v>
+      </c>
+      <c r="D6" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="E6" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F6" t="str">
+        <v>all</v>
+      </c>
+      <c r="G6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H6" t="str">
+        <v>遇到难题先想到「我搞不定」时</v>
+      </c>
+      <c r="I6" t="str">
+        <v>low</v>
+      </c>
+      <c r="J6" t="str">
+        <v>SG_AT_EFFICACY</v>
+      </c>
+      <c r="K6" t="str">
+        <v>效能感不足</v>
+      </c>
+      <c r="L6" t="str">
+        <v>self_growth,efficacy</v>
+      </c>
+      <c r="M6" t="str">
+        <v>SG_EFFICACY</v>
+      </c>
+      <c r="N6" t="str">
+        <v>把已有经验转成可复用的方法</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">回忆一件你处理得还不错的类似事件
+写出当时你具体做了哪三步
+把这三步套用到当前难题上，标出需要调整的部分
+只执行第一步，执行后记录效果</v>
+      </c>
+      <c r="P6" t="str">
+        <v>上次遇到类似情况我是先做了这一步，这次也从这里开始。</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>形成一条可复用的处理路径</v>
+      </c>
+      <c r="R6" t="str">
         <v>15 分钟</v>
       </c>
-      <c r="Q5" t="str">
-        <v>每周 2-3 次，持续 4 周</v>
-      </c>
-      <c r="R5" t="str">
-        <v>14</v>
-      </c>
-      <c r="S5" t="str">
-        <v>有严重抑郁症状的教师应先在心理专员指导下使用</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
-        <v>B</v>
-      </c>
-      <c r="Y5" t="str">
-        <v>Beck 认知疗法教师适应性改编研究（2022）</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>2周后负面自动思维频率下降 &gt;=30%</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>使用2周后负面思维频率未下降且教师反馈无改善</v>
-      </c>
-      <c r="AB5" t="str">
-        <v>打印认知重构工作表</v>
-      </c>
-      <c r="AC5" t="str">
-        <v>认知重构工作表、笔</v>
-      </c>
-      <c r="AD5" t="str">
-        <v>完成的认知重构工作表</v>
-      </c>
-      <c r="AE5" t="str">
-        <v/>
-      </c>
-      <c r="AF5" t="str">
-        <v>自我成长赋能处方库 P18</v>
-      </c>
-      <c r="AG5" t="str">
+      <c r="S6" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T6" t="str">
+        <v>30</v>
+      </c>
+      <c r="U6" t="str">
+        <v>不要拿他人的成功案例替代自己的</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v>C</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>焦点解决短期干预教师应用</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>写出至少三步可执行动作</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>回忆不起任何成功案例（此时改用 SG_RX_003）</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AI6" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH5" t="str">
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>SG_RX_006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>危机求助指引卡</v>
+      </c>
+      <c r="C7" t="str">
+        <v>求助指引</v>
+      </c>
+      <c r="D7" t="str">
+        <v>self_growth</v>
+      </c>
+      <c r="E7" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F7" t="str">
+        <v>all</v>
+      </c>
+      <c r="G7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H7" t="str">
+        <v>出现持续失眠、自伤念头或强烈无意义感时</v>
+      </c>
+      <c r="I7" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="J7" t="str">
+        <v>SG_AT_MEANING</v>
+      </c>
+      <c r="K7" t="str">
+        <v>意义感流失</v>
+      </c>
+      <c r="L7" t="str">
+        <v>self_growth,meaning,crisis</v>
+      </c>
+      <c r="M7" t="str">
+        <v>SG_MEANING</v>
+      </c>
+      <c r="N7" t="str">
+        <v>确保教师知道向谁求助、怎么求助</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">停止当前所有非必要工作
+联系校内心理专员，说明当前状态
+如存在即时危险，拨打 110 或 120
+告知一位可信任的家人或朋友当前情况</v>
+      </c>
+      <c r="P7" t="str">
+        <v>我现在的状态需要一些专业支持，想请你帮我联系一下心理专员。</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>在 24 小时内建立专业支持连接</v>
+      </c>
+      <c r="R7" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S7" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T7" t="str">
+        <v>30</v>
+      </c>
+      <c r="U7" t="str">
+        <v>不得由班主任自行承担危机处置；不得延迟转介</v>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>校园心理危机干预规范</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>完成一次专业联系</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>24 小时内未建立任何联系</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v>自我成长赋能手册v1</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -972,28 +1240,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境</v>
+        <v>离开当前情境，找一个不被</v>
       </c>
       <c r="D2" t="str">
-        <v>暂时离开当前工作环境（办公室、教室），找到一个安静不被打扰的空间</v>
+        <v>离开当前情境，找一个不被打扰的空间</v>
       </c>
       <c r="E2" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>不需要走很远，去走廊尽头或空会议室即可</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>现在先停三分钟，这三分钟只属于你自己。</v>
       </c>
       <c r="I2" t="str">
-        <v>教师已经离开原环境，至少获得3分钟不被干扰的时间</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J2" t="str">
-        <v>如果实在无法离开怎么办？（答：至少转身背对工作区域，闭眼30秒）</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1004,28 +1272,28 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>三轮缓慢呼吸</v>
+        <v>做三轮缓慢呼吸，吸气 4</v>
       </c>
       <c r="D3" t="str">
-        <v>进行三轮缓慢深呼吸：吸气4秒→屏息2秒→呼气6秒。每轮之间自然呼吸10秒</v>
+        <v>做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒</v>
       </c>
       <c r="E3" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>计时器（可选）</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>不要刻意用力呼吸，重点是让呼气比吸气更长</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成了三轮呼吸</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J3" t="str">
-        <v>如果注意力无法集中怎么办？（答：把注意力放在呼气的感觉上，每次走神都重新回来即可）</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1036,25 +1304,25 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>命名此刻的情绪</v>
+        <v>给当下的情绪命名，不评价</v>
       </c>
       <c r="D4" t="str">
-        <v>问自己「我现在感受到的是什么？」——是愤怒、委屈、无力、焦虑、还是别的？给情绪一个名字</v>
+        <v>给当下的情绪命名，不评价</v>
       </c>
       <c r="E4" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>不需要分析原因，只需要命名。如果同时有多种情绪，选最强烈的那一个</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>教师能够说出至少一种情绪的名称</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1068,25 +1336,25 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个最小行动</v>
+        <v>选一个 5 分钟内能完成</v>
       </c>
       <c r="D5" t="str">
-        <v>问自己「接下来5分钟，我能做的最小、最简单的一件事是什么？」选一件，然后做</v>
+        <v>选一个 5 分钟内能完成的最小行动</v>
       </c>
       <c r="E5" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>最小行动的标准：不需要别人配合，不需要准备，立即能做</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>教师选出了至少一个可行的最小行动</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1100,25 +1368,25 @@
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>记录今日能量</v>
+        <v>列出当前所有让你焦虑的事</v>
       </c>
       <c r="D6" t="str">
-        <v>在能量记录卡上记录你今天几个关键时间点的能量状态（1-10分）</v>
+        <v>列出当前所有让你焦虑的事项，不做筛选</v>
       </c>
       <c r="E6" t="str">
-        <v>3分钟</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>能量记录卡</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>保持诚实，不需要美化</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>这件事我会在核实后回复，目前先按约定步骤处理。</v>
       </c>
       <c r="I6" t="str">
-        <v>完成了至少3个时间点的记录</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1132,40 +1400,616 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>识别能量消耗</v>
+        <v>逐项标记为「我能控制」「</v>
       </c>
       <c r="D7" t="str">
-        <v>回顾今天的能量低谷，思考是什么消耗了你的能量</v>
+        <v>逐项标记为「我能控制」「我能影响」「暂时不可控」</v>
       </c>
       <c r="E7" t="str">
-        <v>2分钟</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>不需要找出所有原因，选影响最大的1-2个即可</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>识别出至少1个能量消耗源</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SG_RX_002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>暂时不可控的一栏整体划掉</v>
+      </c>
+      <c r="D8" t="str">
+        <v>暂时不可控的一栏整体划掉，本周不再想它</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SG_RX_002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>从「我能控制」里只挑一项</v>
+      </c>
+      <c r="D9" t="str">
+        <v>从「我能控制」里只挑一项，写清今天的第一步</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SG_RX_003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>约一位信任的同事，明确只</v>
+      </c>
+      <c r="D10" t="str">
+        <v>约一位信任的同事，明确只谈 20 分钟</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H10" t="str">
+        <v>我最近在这个问题上消耗比较大，想请你帮我一起看一下事实和下一步，不需要马上给答案。</v>
+      </c>
+      <c r="I10" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SG_RX_003</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>按「事实—感受—我需要的</v>
+      </c>
+      <c r="D11" t="str">
+        <v>按「事实—感受—我需要的支持」三段说，不要求对方给答案</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SG_RX_003</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>请对方复述一遍你说的事实</v>
+      </c>
+      <c r="D12" t="str">
+        <v>请对方复述一遍你说的事实，确认没有偏差</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SG_RX_003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>约定下一次复盘时间</v>
+      </c>
+      <c r="D13" t="str">
+        <v>约定下一次复盘时间</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SG_RX_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>每天下班前写一句：今天有</v>
+      </c>
+      <c r="D14" t="str">
+        <v>每天下班前写一句：今天有一件事因为我而不一样</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H14" t="str">
+        <v>我今天注意到他主动帮同学捡了书，这在两周前是没有的。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SG_RX_004</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>不追求重大事件，一句问候</v>
+      </c>
+      <c r="D15" t="str">
+        <v>不追求重大事件，一句问候、一次等待都算</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SG_RX_004</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>连续记录七天后回看，圈出</v>
+      </c>
+      <c r="D16" t="str">
+        <v>连续记录七天后回看，圈出最触动你的三条</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SG_RX_004</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>把其中一条讲给一位同事听</v>
+      </c>
+      <c r="D17" t="str">
+        <v>把其中一条讲给一位同事听</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SG_RX_005</v>
+      </c>
+      <c r="B18" t="str">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>回忆一件你处理得还不错的</v>
+      </c>
+      <c r="D18" t="str">
+        <v>回忆一件你处理得还不错的类似事件</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H18" t="str">
+        <v>上次遇到类似情况我是先做了这一步，这次也从这里开始。</v>
+      </c>
+      <c r="I18" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SG_RX_005</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>写出当时你具体做了哪三步</v>
+      </c>
+      <c r="D19" t="str">
+        <v>写出当时你具体做了哪三步</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SG_RX_005</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>把这三步套用到当前难题上</v>
+      </c>
+      <c r="D20" t="str">
+        <v>把这三步套用到当前难题上，标出需要调整的部分</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SG_RX_005</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>只执行第一步，执行后记录</v>
+      </c>
+      <c r="D21" t="str">
+        <v>只执行第一步，执行后记录效果</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SG_RX_006</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>停止当前所有非必要工作</v>
+      </c>
+      <c r="D22" t="str">
+        <v>停止当前所有非必要工作</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H22" t="str">
+        <v>我现在的状态需要一些专业支持，想请你帮我联系一下心理专员。</v>
+      </c>
+      <c r="I22" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SG_RX_006</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>联系校内心理专员，说明当</v>
+      </c>
+      <c r="D23" t="str">
+        <v>联系校内心理专员，说明当前状态</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SG_RX_006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>如存在即时危险，拨打 1</v>
+      </c>
+      <c r="D24" t="str">
+        <v>如存在即时危险，拨打 110 或 120</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SG_RX_006</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>告知一位可信任的家人或朋</v>
+      </c>
+      <c r="D25" t="str">
+        <v>告知一位可信任的家人或朋友当前情况</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1192,76 +2036,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B2" t="str">
-        <v>教师自评抑郁量表得分&gt;=15</v>
+        <v>当事人已在专业干预中</v>
       </c>
       <c r="C2" t="str">
-        <v>block</v>
+        <v>warn</v>
       </c>
       <c r="D2" t="str">
-        <v>抑郁风险较高时应先进行专业心理评估，不可单独依赖呼吸练习</v>
+        <v>已有专业支持时避免重复动员造成压力</v>
       </c>
       <c r="E2" t="str">
-        <v>通知心理专员进行评估</v>
+        <v>与专员确认现有干预方案</v>
       </c>
       <c r="F2" t="str">
-        <v>存在抑郁风险的教师</v>
+        <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SG_RX_004</v>
-      </c>
-      <c r="B3" t="str">
-        <v>教师处于急性危机状态</v>
-      </c>
-      <c r="C3" t="str">
-        <v>block</v>
-      </c>
-      <c r="D3" t="str">
-        <v>急性危机时认知重构类工具可能加重混乱感</v>
-      </c>
-      <c r="E3" t="str">
-        <v>先使用安全稳定化工具，等状态稳定后再使用</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>SG_RX_003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>参与教师超过8人</v>
-      </c>
-      <c r="C4" t="str">
-        <v>warn</v>
-      </c>
-      <c r="D4" t="str">
-        <v>超过8人时小组讨论深度下降，建议拆分小组</v>
-      </c>
-      <c r="E4" t="str">
-        <v>每组控制在4-6人，增加一名引导员</v>
-      </c>
-      <c r="F4" t="str">
-        <v>年级组长</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>自我成长赋能手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/self_growth/tool.xlsx
+++ b/business-libraries/test-data/self_growth/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>三分钟补能法</v>
       </c>
       <c r="C2" t="str">
-        <v>3分钟补能</v>
+        <v>三分钟补能法</v>
       </c>
       <c r="D2" t="str">
         <v>self_growth</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>SG_AT_EXHAUST</v>
+        <v>SG_AT_01</v>
       </c>
       <c r="K2" t="str">
         <v>情绪耗竭</v>
@@ -549,16 +549,13 @@
         <v>self_growth,emotion,pressure</v>
       </c>
       <c r="M2" t="str">
-        <v>SG_EMOTION</v>
+        <v>SG_S1D1</v>
       </c>
       <c r="N2" t="str">
         <v>快速降低主观压力，恢复对当下的控制感</v>
       </c>
-      <c r="O2" t="str" xml:space="preserve">
-        <v xml:space="preserve">离开当前情境，找一个不被打扰的空间
-做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒
-给当下的情绪命名，不评价
-选一个 5 分钟内能完成的最小行动</v>
+      <c r="O2" t="str">
+        <v>离开当前情境，找一个不被打扰的空间；做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒；给当下的情绪命名，不评价；选一个 5 分钟内能完成的最小行动</v>
       </c>
       <c r="P2" t="str">
         <v>现在先停三分钟，这三分钟只属于你自己。</v>
@@ -618,21 +615,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>SG_RX_002</v>
+        <v>SG_RX_02</v>
       </c>
       <c r="B3" t="str">
         <v>压力三分法盘点表</v>
       </c>
       <c r="C3" t="str">
-        <v>三分法</v>
+        <v>压力三分法盘点表</v>
       </c>
       <c r="D3" t="str">
         <v>self_growth</v>
@@ -653,7 +650,7 @@
         <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>SG_AT_BOUNDARY</v>
+        <v>SG_AT_02</v>
       </c>
       <c r="K3" t="str">
         <v>角色边界失守</v>
@@ -662,16 +659,13 @@
         <v>self_growth,boundary</v>
       </c>
       <c r="M3" t="str">
-        <v>SG_BOUNDARY</v>
+        <v>SG_S1D2</v>
       </c>
       <c r="N3" t="str">
         <v>把弥散的压力转成可操作的清单</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">列出当前所有让你焦虑的事项，不做筛选
-逐项标记为「我能控制」「我能影响」「暂时不可控」
-暂时不可控的一栏整体划掉，本周不再想它
-从「我能控制」里只挑一项，写清今天的第一步</v>
+      <c r="O3" t="str">
+        <v>列出当前所有让你焦虑的事项，不做筛选；逐项标记为「我能控制」「我能影响」「暂时不可控」；暂时不可控的一栏整体划掉，本周不再想它；从「我能控制」里只挑一项，写清今天的第一步</v>
       </c>
       <c r="P3" t="str">
         <v>这件事我会在核实后回复，目前先按约定步骤处理。</v>
@@ -731,21 +725,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_03</v>
       </c>
       <c r="B4" t="str">
         <v>同伴结构化复盘</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴复盘</v>
+        <v>同伴结构化复盘</v>
       </c>
       <c r="D4" t="str">
         <v>self_growth</v>
@@ -766,7 +760,7 @@
         <v>high</v>
       </c>
       <c r="J4" t="str">
-        <v>SG_AT_SUPPORT</v>
+        <v>SG_AT_05</v>
       </c>
       <c r="K4" t="str">
         <v>支持系统缺失</v>
@@ -775,16 +769,13 @@
         <v>self_growth,support</v>
       </c>
       <c r="M4" t="str">
-        <v>SG_SUPPORT</v>
+        <v>SG_S1D5</v>
       </c>
       <c r="N4" t="str">
         <v>建立稳定的同伴支持通道</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
-        <v xml:space="preserve">约一位信任的同事，明确只谈 20 分钟
-按「事实—感受—我需要的支持」三段说，不要求对方给答案
-请对方复述一遍你说的事实，确认没有偏差
-约定下一次复盘时间</v>
+      <c r="O4" t="str">
+        <v>约一位信任的同事，明确只谈 20 分钟；按「事实—感受—我需要的支持」三段说，不要求对方给答案；请对方复述一遍你说的事实，确认没有偏差；约定下一次复盘时间</v>
       </c>
       <c r="P4" t="str">
         <v>我最近在这个问题上消耗比较大，想请你帮我一起看一下事实和下一步，不需要马上给答案。</v>
@@ -844,21 +835,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_04</v>
       </c>
       <c r="B5" t="str">
         <v>意义锚点记录</v>
       </c>
       <c r="C5" t="str">
-        <v>意义锚点</v>
+        <v>意义锚点记录</v>
       </c>
       <c r="D5" t="str">
         <v>self_growth</v>
@@ -879,7 +870,7 @@
         <v>high</v>
       </c>
       <c r="J5" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="K5" t="str">
         <v>意义感流失</v>
@@ -888,16 +879,13 @@
         <v>self_growth,meaning</v>
       </c>
       <c r="M5" t="str">
-        <v>SG_MEANING</v>
+        <v>SG_S1D3</v>
       </c>
       <c r="N5" t="str">
         <v>重建工作意义的可见证据</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">每天下班前写一句：今天有一件事因为我而不一样
-不追求重大事件，一句问候、一次等待都算
-连续记录七天后回看，圈出最触动你的三条
-把其中一条讲给一位同事听</v>
+      <c r="O5" t="str">
+        <v>每天下班前写一句：今天有一件事因为我而不一样；不追求重大事件，一句问候、一次等待都算；连续记录七天后回看，圈出最触动你的三条；把其中一条讲给一位同事听</v>
       </c>
       <c r="P5" t="str">
         <v>我今天注意到他主动帮同学捡了书，这在两周前是没有的。</v>
@@ -957,21 +945,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
-        <v>SG_RX_005</v>
+        <v>SG_RX_05</v>
       </c>
       <c r="B6" t="str">
         <v>最小成功案例复演</v>
       </c>
       <c r="C6" t="str">
-        <v>最小复演</v>
+        <v>最小成功案例复演</v>
       </c>
       <c r="D6" t="str">
         <v>self_growth</v>
@@ -992,7 +980,7 @@
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>SG_AT_EFFICACY</v>
+        <v>SG_AT_04</v>
       </c>
       <c r="K6" t="str">
         <v>效能感不足</v>
@@ -1001,16 +989,13 @@
         <v>self_growth,efficacy</v>
       </c>
       <c r="M6" t="str">
-        <v>SG_EFFICACY</v>
+        <v>SG_S1D4</v>
       </c>
       <c r="N6" t="str">
         <v>把已有经验转成可复用的方法</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">回忆一件你处理得还不错的类似事件
-写出当时你具体做了哪三步
-把这三步套用到当前难题上，标出需要调整的部分
-只执行第一步，执行后记录效果</v>
+      <c r="O6" t="str">
+        <v>回忆一件你处理得还不错的类似事件；写出当时你具体做了哪三步；把这三步套用到当前难题上，标出需要调整的部分；只执行第一步，执行后记录效果</v>
       </c>
       <c r="P6" t="str">
         <v>上次遇到类似情况我是先做了这一步，这次也从这里开始。</v>
@@ -1070,21 +1055,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>SG_RX_006</v>
+        <v>SG_RX_06</v>
       </c>
       <c r="B7" t="str">
         <v>危机求助指引卡</v>
       </c>
       <c r="C7" t="str">
-        <v>求助指引</v>
+        <v>危机求助指引卡</v>
       </c>
       <c r="D7" t="str">
         <v>self_growth</v>
@@ -1105,25 +1090,22 @@
         <v>crisis</v>
       </c>
       <c r="J7" t="str">
-        <v>SG_AT_MEANING</v>
+        <v>SG_AT_03</v>
       </c>
       <c r="K7" t="str">
         <v>意义感流失</v>
       </c>
       <c r="L7" t="str">
-        <v>self_growth,meaning,crisis</v>
+        <v>self_growth,meaning</v>
       </c>
       <c r="M7" t="str">
-        <v>SG_MEANING</v>
+        <v>SG_S1D3</v>
       </c>
       <c r="N7" t="str">
         <v>确保教师知道向谁求助、怎么求助</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">停止当前所有非必要工作
-联系校内心理专员，说明当前状态
-如存在即时危险，拨打 110 或 120
-告知一位可信任的家人或朋友当前情况</v>
+      <c r="O7" t="str">
+        <v>停止当前所有非必要工作；联系校内心理专员，说明当前状态；如存在即时危险，拨打 110 或 120；告知一位可信任的家人或朋友当前情况</v>
       </c>
       <c r="P7" t="str">
         <v>我现在的状态需要一些专业支持，想请你帮我联系一下心理专员。</v>
@@ -1183,7 +1165,7 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -1234,13 +1216,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境，找一个不被</v>
+        <v>离开当前情境，找一个不被打扰的空间</v>
       </c>
       <c r="D2" t="str">
         <v>离开当前情境，找一个不被打扰的空间</v>
@@ -1266,13 +1248,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>做三轮缓慢呼吸，吸气 4</v>
+        <v>做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒</v>
       </c>
       <c r="D3" t="str">
         <v>做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒</v>
@@ -1298,7 +1280,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
@@ -1330,13 +1312,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_RX_001</v>
+        <v>SG_RX_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个 5 分钟内能完成</v>
+        <v>选一个 5 分钟内能完成的最小行动</v>
       </c>
       <c r="D5" t="str">
         <v>选一个 5 分钟内能完成的最小行动</v>
@@ -1362,13 +1344,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_RX_002</v>
+        <v>SG_RX_02</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>列出当前所有让你焦虑的事</v>
+        <v>列出当前所有让你焦虑的事项，不做筛选</v>
       </c>
       <c r="D6" t="str">
         <v>列出当前所有让你焦虑的事项，不做筛选</v>
@@ -1394,13 +1376,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_RX_002</v>
+        <v>SG_RX_02</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>逐项标记为「我能控制」「</v>
+        <v>逐项标记为「我能控制」「我能影响」「暂时不可控」</v>
       </c>
       <c r="D7" t="str">
         <v>逐项标记为「我能控制」「我能影响」「暂时不可控」</v>
@@ -1426,13 +1408,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_RX_002</v>
+        <v>SG_RX_02</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>暂时不可控的一栏整体划掉</v>
+        <v>暂时不可控的一栏整体划掉，本周不再想它</v>
       </c>
       <c r="D8" t="str">
         <v>暂时不可控的一栏整体划掉，本周不再想它</v>
@@ -1458,13 +1440,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_RX_002</v>
+        <v>SG_RX_02</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>从「我能控制」里只挑一项</v>
+        <v>从「我能控制」里只挑一项，写清今天的第一步</v>
       </c>
       <c r="D9" t="str">
         <v>从「我能控制」里只挑一项，写清今天的第一步</v>
@@ -1490,13 +1472,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_03</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>约一位信任的同事，明确只</v>
+        <v>约一位信任的同事，明确只谈 20 分钟</v>
       </c>
       <c r="D10" t="str">
         <v>约一位信任的同事，明确只谈 20 分钟</v>
@@ -1522,13 +1504,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_03</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>按「事实—感受—我需要的</v>
+        <v>按「事实—感受—我需要的支持」三段说，不要求对方</v>
       </c>
       <c r="D11" t="str">
         <v>按「事实—感受—我需要的支持」三段说，不要求对方给答案</v>
@@ -1554,13 +1536,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_03</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>请对方复述一遍你说的事实</v>
+        <v>请对方复述一遍你说的事实，确认没有偏差</v>
       </c>
       <c r="D12" t="str">
         <v>请对方复述一遍你说的事实，确认没有偏差</v>
@@ -1586,7 +1568,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_RX_003</v>
+        <v>SG_RX_03</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
@@ -1618,13 +1600,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_04</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>每天下班前写一句：今天有</v>
+        <v>每天下班前写一句：今天有一件事因为我而不一样</v>
       </c>
       <c r="D14" t="str">
         <v>每天下班前写一句：今天有一件事因为我而不一样</v>
@@ -1650,13 +1632,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_04</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>不追求重大事件，一句问候</v>
+        <v>不追求重大事件，一句问候、一次等待都算</v>
       </c>
       <c r="D15" t="str">
         <v>不追求重大事件，一句问候、一次等待都算</v>
@@ -1682,13 +1664,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_04</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>连续记录七天后回看，圈出</v>
+        <v>连续记录七天后回看，圈出最触动你的三条</v>
       </c>
       <c r="D16" t="str">
         <v>连续记录七天后回看，圈出最触动你的三条</v>
@@ -1714,7 +1696,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SG_RX_004</v>
+        <v>SG_RX_04</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
@@ -1746,13 +1728,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SG_RX_005</v>
+        <v>SG_RX_05</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>回忆一件你处理得还不错的</v>
+        <v>回忆一件你处理得还不错的类似事件</v>
       </c>
       <c r="D18" t="str">
         <v>回忆一件你处理得还不错的类似事件</v>
@@ -1778,7 +1760,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SG_RX_005</v>
+        <v>SG_RX_05</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
@@ -1810,13 +1792,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SG_RX_005</v>
+        <v>SG_RX_05</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>把这三步套用到当前难题上</v>
+        <v>把这三步套用到当前难题上，标出需要调整的部分</v>
       </c>
       <c r="D20" t="str">
         <v>把这三步套用到当前难题上，标出需要调整的部分</v>
@@ -1842,13 +1824,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SG_RX_005</v>
+        <v>SG_RX_05</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>只执行第一步，执行后记录</v>
+        <v>只执行第一步，执行后记录效果</v>
       </c>
       <c r="D21" t="str">
         <v>只执行第一步，执行后记录效果</v>
@@ -1874,7 +1856,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SG_RX_006</v>
+        <v>SG_RX_06</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
@@ -1906,13 +1888,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SG_RX_006</v>
+        <v>SG_RX_06</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>联系校内心理专员，说明当</v>
+        <v>联系校内心理专员，说明当前状态</v>
       </c>
       <c r="D23" t="str">
         <v>联系校内心理专员，说明当前状态</v>
@@ -1938,13 +1920,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SG_RX_006</v>
+        <v>SG_RX_06</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>如存在即时危险，拨打 1</v>
+        <v>如存在即时危险，拨打 110 或 120</v>
       </c>
       <c r="D24" t="str">
         <v>如存在即时危险，拨打 110 或 120</v>
@@ -1970,13 +1952,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SG_RX_006</v>
+        <v>SG_RX_06</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>告知一位可信任的家人或朋</v>
+        <v>告知一位可信任的家人或朋友当前情况</v>
       </c>
       <c r="D25" t="str">
         <v>告知一位可信任的家人或朋友当前情况</v>
@@ -2036,7 +2018,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_006</v>
+        <v>SG_RX_06</v>
       </c>
       <c r="B2" t="str">
         <v>当事人已在专业干预中</v>

--- a/business-libraries/test-data/self_growth/tool.xlsx
+++ b/business-libraries/test-data/self_growth/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>SG_RX_01</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>三分钟补能法</v>
       </c>
       <c r="C2" t="str">
-        <v>三分钟补能法</v>
+        <v>3分钟补能</v>
       </c>
       <c r="D2" t="str">
         <v>self_growth</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>SG_AT_01</v>
+        <v>SG_AT_EXHAUST</v>
       </c>
       <c r="K2" t="str">
         <v>情绪耗竭</v>
@@ -549,13 +549,16 @@
         <v>self_growth,emotion,pressure</v>
       </c>
       <c r="M2" t="str">
-        <v>SG_S1D1</v>
+        <v>SG_EMOTION</v>
       </c>
       <c r="N2" t="str">
         <v>快速降低主观压力，恢复对当下的控制感</v>
       </c>
-      <c r="O2" t="str">
-        <v>离开当前情境，找一个不被打扰的空间；做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒；给当下的情绪命名，不评价；选一个 5 分钟内能完成的最小行动</v>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">离开当前情境，找一个不被打扰的空间
+做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒
+给当下的情绪命名，不评价
+选一个 5 分钟内能完成的最小行动</v>
       </c>
       <c r="P2" t="str">
         <v>现在先停三分钟，这三分钟只属于你自己。</v>
@@ -615,21 +618,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_002</v>
       </c>
       <c r="B3" t="str">
         <v>压力三分法盘点表</v>
       </c>
       <c r="C3" t="str">
-        <v>压力三分法盘点表</v>
+        <v>三分法</v>
       </c>
       <c r="D3" t="str">
         <v>self_growth</v>
@@ -650,7 +653,7 @@
         <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>SG_AT_02</v>
+        <v>SG_AT_BOUNDARY</v>
       </c>
       <c r="K3" t="str">
         <v>角色边界失守</v>
@@ -659,13 +662,16 @@
         <v>self_growth,boundary</v>
       </c>
       <c r="M3" t="str">
-        <v>SG_S1D2</v>
+        <v>SG_BOUNDARY</v>
       </c>
       <c r="N3" t="str">
         <v>把弥散的压力转成可操作的清单</v>
       </c>
-      <c r="O3" t="str">
-        <v>列出当前所有让你焦虑的事项，不做筛选；逐项标记为「我能控制」「我能影响」「暂时不可控」；暂时不可控的一栏整体划掉，本周不再想它；从「我能控制」里只挑一项，写清今天的第一步</v>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">列出当前所有让你焦虑的事项，不做筛选
+逐项标记为「我能控制」「我能影响」「暂时不可控」
+暂时不可控的一栏整体划掉，本周不再想它
+从「我能控制」里只挑一项，写清今天的第一步</v>
       </c>
       <c r="P3" t="str">
         <v>这件事我会在核实后回复，目前先按约定步骤处理。</v>
@@ -725,21 +731,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>SG_RX_03</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="B4" t="str">
         <v>同伴结构化复盘</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴结构化复盘</v>
+        <v>同伴复盘</v>
       </c>
       <c r="D4" t="str">
         <v>self_growth</v>
@@ -760,7 +766,7 @@
         <v>high</v>
       </c>
       <c r="J4" t="str">
-        <v>SG_AT_05</v>
+        <v>SG_AT_SUPPORT</v>
       </c>
       <c r="K4" t="str">
         <v>支持系统缺失</v>
@@ -769,13 +775,16 @@
         <v>self_growth,support</v>
       </c>
       <c r="M4" t="str">
-        <v>SG_S1D5</v>
+        <v>SG_SUPPORT</v>
       </c>
       <c r="N4" t="str">
         <v>建立稳定的同伴支持通道</v>
       </c>
-      <c r="O4" t="str">
-        <v>约一位信任的同事，明确只谈 20 分钟；按「事实—感受—我需要的支持」三段说，不要求对方给答案；请对方复述一遍你说的事实，确认没有偏差；约定下一次复盘时间</v>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">约一位信任的同事，明确只谈 20 分钟
+按「事实—感受—我需要的支持」三段说，不要求对方给答案
+请对方复述一遍你说的事实，确认没有偏差
+约定下一次复盘时间</v>
       </c>
       <c r="P4" t="str">
         <v>我最近在这个问题上消耗比较大，想请你帮我一起看一下事实和下一步，不需要马上给答案。</v>
@@ -835,21 +844,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="B5" t="str">
         <v>意义锚点记录</v>
       </c>
       <c r="C5" t="str">
-        <v>意义锚点记录</v>
+        <v>意义锚点</v>
       </c>
       <c r="D5" t="str">
         <v>self_growth</v>
@@ -870,7 +879,7 @@
         <v>high</v>
       </c>
       <c r="J5" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="K5" t="str">
         <v>意义感流失</v>
@@ -879,13 +888,16 @@
         <v>self_growth,meaning</v>
       </c>
       <c r="M5" t="str">
-        <v>SG_S1D3</v>
+        <v>SG_MEANING</v>
       </c>
       <c r="N5" t="str">
         <v>重建工作意义的可见证据</v>
       </c>
-      <c r="O5" t="str">
-        <v>每天下班前写一句：今天有一件事因为我而不一样；不追求重大事件，一句问候、一次等待都算；连续记录七天后回看，圈出最触动你的三条；把其中一条讲给一位同事听</v>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">每天下班前写一句：今天有一件事因为我而不一样
+不追求重大事件，一句问候、一次等待都算
+连续记录七天后回看，圈出最触动你的三条
+把其中一条讲给一位同事听</v>
       </c>
       <c r="P5" t="str">
         <v>我今天注意到他主动帮同学捡了书，这在两周前是没有的。</v>
@@ -945,21 +957,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>SG_RX_05</v>
+        <v>SG_RX_005</v>
       </c>
       <c r="B6" t="str">
         <v>最小成功案例复演</v>
       </c>
       <c r="C6" t="str">
-        <v>最小成功案例复演</v>
+        <v>最小复演</v>
       </c>
       <c r="D6" t="str">
         <v>self_growth</v>
@@ -980,7 +992,7 @@
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>SG_AT_04</v>
+        <v>SG_AT_EFFICACY</v>
       </c>
       <c r="K6" t="str">
         <v>效能感不足</v>
@@ -989,13 +1001,16 @@
         <v>self_growth,efficacy</v>
       </c>
       <c r="M6" t="str">
-        <v>SG_S1D4</v>
+        <v>SG_EFFICACY</v>
       </c>
       <c r="N6" t="str">
         <v>把已有经验转成可复用的方法</v>
       </c>
-      <c r="O6" t="str">
-        <v>回忆一件你处理得还不错的类似事件；写出当时你具体做了哪三步；把这三步套用到当前难题上，标出需要调整的部分；只执行第一步，执行后记录效果</v>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">回忆一件你处理得还不错的类似事件
+写出当时你具体做了哪三步
+把这三步套用到当前难题上，标出需要调整的部分
+只执行第一步，执行后记录效果</v>
       </c>
       <c r="P6" t="str">
         <v>上次遇到类似情况我是先做了这一步，这次也从这里开始。</v>
@@ -1055,21 +1070,21 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>SG_RX_06</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B7" t="str">
         <v>危机求助指引卡</v>
       </c>
       <c r="C7" t="str">
-        <v>危机求助指引卡</v>
+        <v>求助指引</v>
       </c>
       <c r="D7" t="str">
         <v>self_growth</v>
@@ -1090,22 +1105,25 @@
         <v>crisis</v>
       </c>
       <c r="J7" t="str">
-        <v>SG_AT_03</v>
+        <v>SG_AT_MEANING</v>
       </c>
       <c r="K7" t="str">
         <v>意义感流失</v>
       </c>
       <c r="L7" t="str">
-        <v>self_growth,meaning</v>
+        <v>self_growth,meaning,crisis</v>
       </c>
       <c r="M7" t="str">
-        <v>SG_S1D3</v>
+        <v>SG_MEANING</v>
       </c>
       <c r="N7" t="str">
         <v>确保教师知道向谁求助、怎么求助</v>
       </c>
-      <c r="O7" t="str">
-        <v>停止当前所有非必要工作；联系校内心理专员，说明当前状态；如存在即时危险，拨打 110 或 120；告知一位可信任的家人或朋友当前情况</v>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">停止当前所有非必要工作
+联系校内心理专员，说明当前状态
+如存在即时危险，拨打 110 或 120
+告知一位可信任的家人或朋友当前情况</v>
       </c>
       <c r="P7" t="str">
         <v>我现在的状态需要一些专业支持，想请你帮我联系一下心理专员。</v>
@@ -1165,7 +1183,7 @@
         <v>自我成长赋能手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -1216,13 +1234,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_01</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境，找一个不被打扰的空间</v>
+        <v>离开当前情境，找一个不被</v>
       </c>
       <c r="D2" t="str">
         <v>离开当前情境，找一个不被打扰的空间</v>
@@ -1248,13 +1266,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SG_RX_01</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒</v>
+        <v>做三轮缓慢呼吸，吸气 4</v>
       </c>
       <c r="D3" t="str">
         <v>做三轮缓慢呼吸，吸气 4 秒、呼气 6 秒</v>
@@ -1280,7 +1298,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SG_RX_01</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
@@ -1312,13 +1330,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SG_RX_01</v>
+        <v>SG_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个 5 分钟内能完成的最小行动</v>
+        <v>选一个 5 分钟内能完成</v>
       </c>
       <c r="D5" t="str">
         <v>选一个 5 分钟内能完成的最小行动</v>
@@ -1344,13 +1362,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>列出当前所有让你焦虑的事项，不做筛选</v>
+        <v>列出当前所有让你焦虑的事</v>
       </c>
       <c r="D6" t="str">
         <v>列出当前所有让你焦虑的事项，不做筛选</v>
@@ -1376,13 +1394,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>逐项标记为「我能控制」「我能影响」「暂时不可控」</v>
+        <v>逐项标记为「我能控制」「</v>
       </c>
       <c r="D7" t="str">
         <v>逐项标记为「我能控制」「我能影响」「暂时不可控」</v>
@@ -1408,13 +1426,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_002</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>暂时不可控的一栏整体划掉，本周不再想它</v>
+        <v>暂时不可控的一栏整体划掉</v>
       </c>
       <c r="D8" t="str">
         <v>暂时不可控的一栏整体划掉，本周不再想它</v>
@@ -1440,13 +1458,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SG_RX_02</v>
+        <v>SG_RX_002</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>从「我能控制」里只挑一项，写清今天的第一步</v>
+        <v>从「我能控制」里只挑一项</v>
       </c>
       <c r="D9" t="str">
         <v>从「我能控制」里只挑一项，写清今天的第一步</v>
@@ -1472,13 +1490,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SG_RX_03</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>约一位信任的同事，明确只谈 20 分钟</v>
+        <v>约一位信任的同事，明确只</v>
       </c>
       <c r="D10" t="str">
         <v>约一位信任的同事，明确只谈 20 分钟</v>
@@ -1504,13 +1522,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SG_RX_03</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>按「事实—感受—我需要的支持」三段说，不要求对方</v>
+        <v>按「事实—感受—我需要的</v>
       </c>
       <c r="D11" t="str">
         <v>按「事实—感受—我需要的支持」三段说，不要求对方给答案</v>
@@ -1536,13 +1554,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SG_RX_03</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>请对方复述一遍你说的事实，确认没有偏差</v>
+        <v>请对方复述一遍你说的事实</v>
       </c>
       <c r="D12" t="str">
         <v>请对方复述一遍你说的事实，确认没有偏差</v>
@@ -1568,7 +1586,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SG_RX_03</v>
+        <v>SG_RX_003</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
@@ -1600,13 +1618,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>每天下班前写一句：今天有一件事因为我而不一样</v>
+        <v>每天下班前写一句：今天有</v>
       </c>
       <c r="D14" t="str">
         <v>每天下班前写一句：今天有一件事因为我而不一样</v>
@@ -1632,13 +1650,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>不追求重大事件，一句问候、一次等待都算</v>
+        <v>不追求重大事件，一句问候</v>
       </c>
       <c r="D15" t="str">
         <v>不追求重大事件，一句问候、一次等待都算</v>
@@ -1664,13 +1682,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>连续记录七天后回看，圈出最触动你的三条</v>
+        <v>连续记录七天后回看，圈出</v>
       </c>
       <c r="D16" t="str">
         <v>连续记录七天后回看，圈出最触动你的三条</v>
@@ -1696,7 +1714,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SG_RX_04</v>
+        <v>SG_RX_004</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
@@ -1728,13 +1746,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SG_RX_05</v>
+        <v>SG_RX_005</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>回忆一件你处理得还不错的类似事件</v>
+        <v>回忆一件你处理得还不错的</v>
       </c>
       <c r="D18" t="str">
         <v>回忆一件你处理得还不错的类似事件</v>
@@ -1760,7 +1778,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SG_RX_05</v>
+        <v>SG_RX_005</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
@@ -1792,13 +1810,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SG_RX_05</v>
+        <v>SG_RX_005</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>把这三步套用到当前难题上，标出需要调整的部分</v>
+        <v>把这三步套用到当前难题上</v>
       </c>
       <c r="D20" t="str">
         <v>把这三步套用到当前难题上，标出需要调整的部分</v>
@@ -1824,13 +1842,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SG_RX_05</v>
+        <v>SG_RX_005</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>只执行第一步，执行后记录效果</v>
+        <v>只执行第一步，执行后记录</v>
       </c>
       <c r="D21" t="str">
         <v>只执行第一步，执行后记录效果</v>
@@ -1856,7 +1874,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SG_RX_06</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
@@ -1888,13 +1906,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SG_RX_06</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>联系校内心理专员，说明当前状态</v>
+        <v>联系校内心理专员，说明当</v>
       </c>
       <c r="D23" t="str">
         <v>联系校内心理专员，说明当前状态</v>
@@ -1920,13 +1938,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SG_RX_06</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>如存在即时危险，拨打 110 或 120</v>
+        <v>如存在即时危险，拨打 1</v>
       </c>
       <c r="D24" t="str">
         <v>如存在即时危险，拨打 110 或 120</v>
@@ -1952,13 +1970,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SG_RX_06</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>告知一位可信任的家人或朋友当前情况</v>
+        <v>告知一位可信任的家人或朋</v>
       </c>
       <c r="D25" t="str">
         <v>告知一位可信任的家人或朋友当前情况</v>
@@ -2018,7 +2036,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SG_RX_06</v>
+        <v>SG_RX_006</v>
       </c>
       <c r="B2" t="str">
         <v>当事人已在专业干预中</v>
